--- a/laporan_padel_dki_jakarta_2026-09-24.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-24.xlsx
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp3.350.000</t>
+          <t>Rp3.850.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp7.050.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.314.000</t>
+          <t>Rp1.614.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>72</v>
       </c>
       <c r="D24" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp2.440.000</t>
+          <t>Rp2.565.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>51</v>
       </c>
       <c r="D25" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.875.000</t>
+          <t>Rp1.725.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>120</v>
       </c>
       <c r="D76" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp4.310.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>54</v>
       </c>
       <c r="D80" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.450.000</t>
+          <t>Rp5.050.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>16</v>
       </c>
       <c r="D22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp997.000</t>
+          <t>Rp1.296.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4687,16 +4687,16 @@
         <v>45</v>
       </c>
       <c r="D40" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp3.575.000</t>
+          <t>Rp4.125.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>80</v>
       </c>
       <c r="D51" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp4.875.000</t>
+          <t>Rp5.125.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>84</v>
       </c>
       <c r="D52" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp6.075.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp283.000</t>
+          <t>Rp354.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.635.000</t>
+          <t>Rp10.860.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp15.018.500</t>
+          <t>Rp15.578.500</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.875.000</t>
+          <t>Rp6.335.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp13.663.000</t>
+          <t>Rp8.951.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>16</v>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp999.000</t>
+          <t>Rp1.319.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>75</v>
       </c>
       <c r="D30" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.275.000</t>
+          <t>Rp1.275.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>85</v>
       </c>
       <c r="D36" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp6.100.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>80</v>
       </c>
       <c r="D41" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp550.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>112</v>
       </c>
       <c r="D43" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp8.465.000</t>
+          <t>Rp8.730.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>108</v>
       </c>
       <c r="D47" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp550.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp370.000</t>
+          <t>Rp925.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp4.440.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp2.279.000</t>
+          <t>Rp2.429.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-24.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-24.xlsx
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp11.410.000</t>
+          <t>Rp11.910.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp3.650.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp12.222.000</t>
+          <t>Rp12.497.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>144</v>
       </c>
       <c r="D16" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.152.000</t>
+          <t>Rp2.880.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>168</v>
       </c>
       <c r="D21" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp14.000.000</t>
+          <t>Rp14.875.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>102</v>
       </c>
       <c r="D22" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>51</v>
       </c>
       <c r="D25" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.725.000</t>
+          <t>Rp1.575.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>68</v>
       </c>
       <c r="D30" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp498.000</t>
+          <t>Rp798.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>85</v>
       </c>
       <c r="D32" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.943.000</t>
+          <t>Rp2.143.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>72</v>
       </c>
       <c r="D34" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.270.000</t>
+          <t>Rp3.152.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.920.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>180</v>
       </c>
       <c r="D42" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp12.400.000</t>
+          <t>Rp12.850.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>60</v>
       </c>
       <c r="D44" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.499.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp5.472.000</t>
+          <t>Rp5.184.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp1.672.000</t>
+          <t>Rp1.848.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>48</v>
       </c>
       <c r="D56" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp2.010.000</t>
+          <t>Rp2.210.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp2.675.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>112</v>
       </c>
       <c r="D60" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp2.192.000</t>
+          <t>Rp1.793.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp8.520.000</t>
+          <t>Rp8.620.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>68</v>
       </c>
       <c r="D62" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp2.470.000</t>
+          <t>Rp2.830.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>176</v>
       </c>
       <c r="D69" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp4.381.500</t>
+          <t>Rp4.879.500</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp640.000</t>
+          <t>Rp980.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>108</v>
       </c>
       <c r="D77" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp2.875.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>80</v>
       </c>
       <c r="D79" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp4.225.000</t>
+          <t>Rp4.625.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>80</v>
       </c>
       <c r="D86" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp4.332.000</t>
+          <t>Rp4.531.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>138</v>
       </c>
       <c r="D87" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp7.850.000</t>
+          <t>Rp8.300.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>36</v>
       </c>
       <c r="D90" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp150.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>112</v>
       </c>
       <c r="D95" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp3.030.000</t>
+          <t>Rp3.230.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>68</v>
       </c>
       <c r="D96" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp4.005.000</t>
+          <t>Rp4.130.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>120</v>
       </c>
       <c r="D3" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp14.125.003</t>
+          <t>Rp14.635.004</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp5.134.000</t>
+          <t>Rp7.312.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>51</v>
       </c>
       <c r="D6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp590.000</t>
+          <t>Rp770.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.995.000</t>
+          <t>Rp7.195.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.849.000</t>
+          <t>Rp2.245.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>64</v>
       </c>
       <c r="D11" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp10.875.000</t>
+          <t>Rp11.250.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp5.050.000</t>
+          <t>Rp5.650.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.315.000</t>
+          <t>Rp2.790.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rp80.000 - Rp120.000</t>
+          <t>Rp80.000 - Rp115.000</t>
         </is>
       </c>
     </row>
@@ -4346,16 +4346,16 @@
         <v>170</v>
       </c>
       <c r="D29" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp13.915.000</t>
+          <t>Rp14.090.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4408,16 +4408,16 @@
         <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4501,16 +4501,16 @@
         <v>90</v>
       </c>
       <c r="D34" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp5.800.000</t>
+          <t>Rp5.300.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4563,16 +4563,16 @@
         <v>70</v>
       </c>
       <c r="D36" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp4.020.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp175.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -5028,16 +5028,16 @@
         <v>80</v>
       </c>
       <c r="D51" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp5.125.000</t>
+          <t>Rp5.500.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>72</v>
       </c>
       <c r="D53" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp8.424.000</t>
+          <t>Rp9.216.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>54</v>
       </c>
       <c r="D54" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp8.300.000</t>
+          <t>Rp7.500.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>60</v>
       </c>
       <c r="D55" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp4.850.000</t>
+          <t>Rp5.350.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>36</v>
       </c>
       <c r="D64" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp2.310.000</t>
+          <t>Rp2.590.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>102</v>
       </c>
       <c r="D67" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp6.237.000</t>
+          <t>Rp6.831.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>72</v>
       </c>
       <c r="D68" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp5.950.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp38.450.000</t>
+          <t>Rp35.850.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp9.615.000</t>
+          <t>Rp10.185.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.090.000</t>
+          <t>Rp4.220.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp5.695.000</t>
+          <t>Rp5.820.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp7.150.000</t>
+          <t>Rp7.390.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.248.000</t>
+          <t>Rp1.416.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6370,16 +6370,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp10.240.000</t>
+          <t>Rp10.640.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp12.605.000</t>
+          <t>Rp13.215.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp10.500.000</t>
+          <t>Rp11.375.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp7.569.000</t>
+          <t>Rp8.127.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.125.000</t>
+          <t>Rp6.625.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp12.200.000</t>
+          <t>Rp13.300.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp525.000</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp3.390.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>57</v>
       </c>
       <c r="D29" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp6.690.000</t>
+          <t>Rp6.910.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>75</v>
       </c>
       <c r="D30" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.275.000</t>
+          <t>Rp1.825.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.815.000</t>
+          <t>Rp3.640.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp9.435.000</t>
+          <t>Rp9.190.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp10.425.000</t>
+          <t>Rp11.125.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp24.150.000</t>
+          <t>Rp25.350.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>112</v>
       </c>
       <c r="D40" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.749.000</t>
+          <t>Rp2.549.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>112</v>
       </c>
       <c r="D43" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp8.730.000</t>
+          <t>Rp8.955.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp23.300.000</t>
+          <t>Rp23.400.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp4.775.000</t>
+          <t>Rp5.150.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>48</v>
       </c>
       <c r="D50" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7971,16 +7971,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.140.000</t>
+          <t>Rp10.690.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.960.000</t>
+          <t>Rp2.480.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>88</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp4.982.000</t>
+          <t>Rp5.580.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.900.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp3.625.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp20.720.000</t>
+          <t>Rp21.020.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>64</v>
       </c>
       <c r="D23" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.835.000</t>
+          <t>Rp4.095.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.440.000</t>
+          <t>Rp4.815.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.150.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp5.166.000</t>
+          <t>Rp4.944.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp2.535.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>112</v>
       </c>
       <c r="D36" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.754.000</t>
+          <t>Rp4.854.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp338.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-24.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-24.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.860.000</t>
+          <t>Rp1.960.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp3.025.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.980.000</t>
+          <t>Rp3.776.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.767.984</t>
+          <t>Rp7.211.984</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.650.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp12.497.000</t>
+          <t>Rp13.047.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.614.000</t>
+          <t>Rp1.833.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>168</v>
       </c>
       <c r="D21" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp14.875.000</t>
+          <t>Rp15.373.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>72</v>
       </c>
       <c r="D24" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp2.565.000</t>
+          <t>Rp2.815.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>68</v>
       </c>
       <c r="D30" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp798.000</t>
+          <t>Rp1.018.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>64</v>
       </c>
       <c r="D31" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.473.000</t>
+          <t>Rp1.897.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>68</v>
       </c>
       <c r="D35" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>64</v>
       </c>
       <c r="D37" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.890.000</t>
+          <t>Rp5.060.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1629,16 +1629,16 @@
         <v>72</v>
       </c>
       <c r="D39" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.260.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.795.000</t>
+          <t>Rp2.965.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>198</v>
       </c>
       <c r="D43" t="n">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>96</v>
       </c>
       <c r="D47" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp3.470.000</t>
+          <t>Rp3.668.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp5.184.000</t>
+          <t>Rp6.048.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>48</v>
       </c>
       <c r="D56" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp2.210.000</t>
+          <t>Rp2.095.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>36</v>
       </c>
       <c r="D59" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.090.000</t>
+          <t>Rp1.239.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>112</v>
       </c>
       <c r="D60" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp1.793.000</t>
+          <t>Rp2.191.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp8.620.000</t>
+          <t>Rp8.940.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>176</v>
       </c>
       <c r="D69" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp4.879.500</t>
+          <t>Rp6.075.500</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp3.681.000</t>
+          <t>Rp3.951.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>68</v>
       </c>
       <c r="D71" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp980.000</t>
+          <t>Rp1.205.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>120</v>
       </c>
       <c r="D76" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp4.310.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>108</v>
       </c>
       <c r="D77" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>80</v>
       </c>
       <c r="D79" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp4.625.000</t>
+          <t>Rp5.025.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>36</v>
       </c>
       <c r="D81" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp2.175.000</t>
+          <t>Rp2.431.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3024,16 +3024,16 @@
         <v>96</v>
       </c>
       <c r="D84" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>36</v>
       </c>
       <c r="D85" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp2.520.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>80</v>
       </c>
       <c r="D86" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp4.531.000</t>
+          <t>Rp4.282.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>138</v>
       </c>
       <c r="D87" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp8.300.000</t>
+          <t>Rp8.750.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>90</v>
       </c>
       <c r="D88" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>112</v>
       </c>
       <c r="D89" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp4.120.000</t>
+          <t>Rp4.480.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>36</v>
       </c>
       <c r="D90" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp290.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3272,16 +3272,16 @@
         <v>36</v>
       </c>
       <c r="D92" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp1.012.000</t>
+          <t>Rp1.111.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>112</v>
       </c>
       <c r="D95" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp3.230.000</t>
+          <t>Rp3.870.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp7.312.000</t>
+          <t>Rp9.490.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3630,14 +3630,14 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D6" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rp180.000 - Rp295.000</t>
+          <t>Rp100.000 - Rp295.000</t>
         </is>
       </c>
     </row>
@@ -3664,16 +3664,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp7.195.000</t>
+          <t>Rp7.595.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp7.370.000</t>
+          <t>Rp7.765.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.960.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>105</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp11.100.000</t>
+          <t>Rp14.050.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp7.155.000</t>
+          <t>Rp7.560.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp5.650.000</t>
+          <t>Rp6.475.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp3.790.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>170</v>
       </c>
       <c r="D29" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp14.090.000</t>
+          <t>Rp15.090.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4563,16 +4563,16 @@
         <v>70</v>
       </c>
       <c r="D36" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.020.000</t>
+          <t>Rp4.270.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>32</v>
       </c>
       <c r="D41" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4811,16 +4811,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>64</v>
       </c>
       <c r="D45" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>80</v>
       </c>
       <c r="D51" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp5.500.000</t>
+          <t>Rp5.875.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>84</v>
       </c>
       <c r="D52" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp6.075.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>54</v>
       </c>
       <c r="D54" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp7.500.000</t>
+          <t>Rp8.300.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>60</v>
       </c>
       <c r="D55" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp5.350.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>128</v>
       </c>
       <c r="D58" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp6.600.000</t>
+          <t>Rp6.950.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp354.000</t>
+          <t>Rp407.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>72</v>
       </c>
       <c r="D68" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp6.300.000</t>
+          <t>Rp6.650.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp10.450.000</t>
+          <t>Rp11.650.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>30</v>
       </c>
       <c r="D71" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5730,16 +5730,16 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.160.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5761,16 +5761,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp19.910.000</t>
+          <t>Rp22.000.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.450.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp35.850.000</t>
+          <t>Rp36.250.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp5.520.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.429.000</t>
+          <t>Rp3.079.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.220.000</t>
+          <t>Rp4.520.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp7.390.000</t>
+          <t>Rp8.850.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.416.000</t>
+          <t>Rp1.644.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>68</v>
       </c>
       <c r="D20" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp8.030.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6370,16 +6370,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp10.640.000</t>
+          <t>Rp9.140.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.860.000</t>
+          <t>Rp11.310.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp665.000</t>
+          <t>Rp734.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp13.215.000</t>
+          <t>Rp13.410.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp11.375.000</t>
+          <t>Rp12.075.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>102</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp9.078.000</t>
+          <t>Rp9.314.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp15.578.500</t>
+          <t>Rp15.018.500</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.335.000</t>
+          <t>Rp6.795.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.625.000</t>
+          <t>Rp7.025.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp5.818.000</t>
+          <t>Rp5.906.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp13.300.000</t>
+          <t>Rp12.250.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp8.951.000</t>
+          <t>Rp9.250.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>16</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp1.319.000</t>
+          <t>Rp1.619.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>75</v>
       </c>
       <c r="D30" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.825.000</t>
+          <t>Rp1.275.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp11.125.000</t>
+          <t>Rp12.450.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>34</v>
       </c>
       <c r="D37" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.728.000</t>
+          <t>Rp2.304.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp25.350.000</t>
+          <t>Rp26.550.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>112</v>
       </c>
       <c r="D43" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp8.955.000</t>
+          <t>Rp10.015.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>174</v>
       </c>
       <c r="D44" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp23.400.000</t>
+          <t>Rp25.000.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>36</v>
       </c>
       <c r="D46" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp7.500.000</t>
+          <t>Rp8.000.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>108</v>
       </c>
       <c r="D47" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.150.000</t>
+          <t>Rp6.025.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>48</v>
       </c>
       <c r="D50" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp5.580.000</t>
+          <t>Rp5.879.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.540.000</t>
+          <t>Rp1.720.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.945.000</t>
+          <t>Rp6.690.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.625.000</t>
+          <t>Rp3.725.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp540.000</t>
+          <t>Rp810.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp6.318.000</t>
+          <t>Rp4.368.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp21.020.000</t>
+          <t>Rp22.420.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.815.000</t>
+          <t>Rp5.010.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp5.675.000</t>
+          <t>Rp5.925.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp2.860.000</t>
+          <t>Rp3.430.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.535.000</t>
+          <t>Rp1.945.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp4.960.000</t>
+          <t>Rp3.960.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp338.000</t>
+          <t>Rp676.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>72</v>
       </c>
       <c r="D41" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.194.000</t>
+          <t>Rp1.791.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-24.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-24.xlsx
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp13.820.000</t>
+          <t>Rp12.820.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.776.000</t>
+          <t>Rp3.179.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp2.675.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>112</v>
       </c>
       <c r="D60" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp2.191.000</t>
+          <t>Rp2.241.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp3.951.000</t>
+          <t>Rp3.681.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>120</v>
       </c>
       <c r="D76" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.780.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>138</v>
       </c>
       <c r="D87" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp8.750.000</t>
+          <t>Rp9.200.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>112</v>
       </c>
       <c r="D89" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp4.480.000</t>
+          <t>Rp4.120.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>112</v>
       </c>
       <c r="D95" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp3.870.000</t>
+          <t>Rp4.070.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp9.490.000</t>
+          <t>Rp10.268.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>14</v>
       </c>
       <c r="D35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>60</v>
       </c>
       <c r="D55" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp407.000</t>
+          <t>Rp469.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>72</v>
       </c>
       <c r="D68" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp6.650.000</t>
+          <t>Rp5.950.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp5.820.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>68</v>
       </c>
       <c r="D20" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp8.030.000</t>
+          <t>Rp7.480.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6370,16 +6370,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp9.140.000</t>
+          <t>Rp9.060.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp6.100.000</t>
+          <t>Rp6.850.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>75</v>
       </c>
       <c r="D30" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.275.000</t>
+          <t>Rp1.825.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp12.450.000</t>
+          <t>Rp12.750.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>102</v>
       </c>
       <c r="D35" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.710.000</t>
+          <t>Rp2.479.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp6.025.000</t>
+          <t>Rp6.200.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.720.000</t>
+          <t>Rp1.980.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp420.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.010.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.572.000</t>
+          <t>Rp1.771.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>34</v>
       </c>
       <c r="D33" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp1.320.000</t>
+          <t>Rp1.900.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.540.000</t>
+          <t>Rp3.065.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-24.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-24.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.960.000</t>
+          <t>Rp2.120.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1192,14 +1192,14 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D25" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp225.000</t>
+          <t>Rp40.000 - Rp225.000</t>
         </is>
       </c>
     </row>
@@ -1474,16 +1474,16 @@
         <v>72</v>
       </c>
       <c r="D34" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.152.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp6.300.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>198</v>
       </c>
       <c r="D43" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp3.681.000</t>
+          <t>Rp3.781.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp1.205.000</t>
+          <t>Rp1.355.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>108</v>
       </c>
       <c r="D77" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp3.325.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>112</v>
       </c>
       <c r="D95" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp4.070.000</t>
+          <t>Rp4.320.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>120</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp14.635.004</t>
+          <t>Rp14.920.004</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.245.000</t>
+          <t>Rp2.444.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp6.475.000</t>
+          <t>Rp6.875.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>54</v>
       </c>
       <c r="D42" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.110.000</t>
+          <t>Rp2.295.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>77</v>
       </c>
       <c r="D46" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp9.100.000</t>
+          <t>Rp9.750.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp469.000</t>
+          <t>Rp540.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>102</v>
       </c>
       <c r="D67" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp6.831.000</t>
+          <t>Rp7.128.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.200.000</t>
+          <t>Rp7.950.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp4.375.000</t>
+          <t>Rp4.575.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.520.000</t>
+          <t>Rp4.140.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp5.800.000</t>
+          <t>Rp6.920.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp734.000</t>
+          <t>Rp872.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.675.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp15.018.500</t>
+          <t>Rp15.255.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp22.800.000</t>
+          <t>Rp23.400.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.640.000</t>
+          <t>Rp3.765.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp12.750.000</t>
+          <t>Rp13.150.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp26.550.000</t>
+          <t>Rp27.235.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7940,16 +7940,16 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.790.000</t>
+          <t>Rp2.945.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.690.000</t>
+          <t>Rp6.540.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp2.429.000</t>
+          <t>Rp2.528.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
